--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20221.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -79,25 +79,16 @@
     <t>ZARATE</t>
   </si>
   <si>
-    <t>VERA</t>
-  </si>
-  <si>
     <t>VICENTE</t>
   </si>
   <si>
     <t>VERGEL</t>
   </si>
   <si>
-    <t>PAZOS</t>
-  </si>
-  <si>
     <t>AMYRA NAHOMY</t>
   </si>
   <si>
     <t>PAULINA</t>
-  </si>
-  <si>
-    <t>CARLA DANIELA</t>
   </si>
 </sst>
 </file>
@@ -550,19 +541,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -664,7 +655,7 @@
         <v>40</v>
       </c>
       <c r="E4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -775,19 +766,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -797,7 +788,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -835,10 +826,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -858,10 +849,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -871,29 +862,6 @@
       </c>
       <c r="G3">
         <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>18330051920189</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20221.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20221.xlsx
@@ -489,19 +489,19 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G2">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -515,19 +515,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -541,10 +541,10 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <v>32</v>
@@ -553,7 +553,7 @@
         <v>80</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -606,16 +606,19 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>91.89</v>
+      </c>
+      <c r="H2">
+        <v>9.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -629,16 +632,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="E3">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>81.08</v>
+      </c>
+      <c r="H3">
+        <v>9.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -652,16 +658,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E4">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="H4">
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -714,16 +723,16 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G2">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="H2">
         <v>9.4</v>
@@ -740,19 +749,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -766,10 +775,10 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <v>32</v>
@@ -778,7 +787,7 @@
         <v>80</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20221.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20221.xlsx
@@ -606,16 +606,16 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>91.89</v>
+        <v>94.59</v>
       </c>
       <c r="H2">
         <v>9.5</v>
@@ -632,19 +632,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>81.08</v>
+        <v>97.3</v>
       </c>
       <c r="H3">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -658,19 +658,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -735,7 +735,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -761,7 +761,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -787,7 +787,7 @@
         <v>80</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20221.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20221.xlsx
@@ -606,19 +606,19 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G2">
-        <v>94.59</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -632,19 +632,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20221.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20221.xlsx
@@ -870,7 +870,7 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20221.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -76,16 +76,34 @@
     <t>BRETON</t>
   </si>
   <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>ZARATE</t>
   </si>
   <si>
     <t>VICENTE</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>VERGEL</t>
   </si>
   <si>
     <t>AMYRA NAHOMY</t>
+  </si>
+  <si>
+    <t>ASTRID</t>
+  </si>
+  <si>
+    <t>ITZEL ISABEL</t>
   </si>
   <si>
     <t>PAULINA</t>
@@ -538,10 +556,10 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>8</v>
@@ -550,7 +568,7 @@
         <v>32</v>
       </c>
       <c r="G4">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="H4">
         <v>7.6</v>
@@ -655,10 +673,10 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>8</v>
@@ -667,7 +685,7 @@
         <v>32</v>
       </c>
       <c r="G4">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="H4">
         <v>7.6</v>
@@ -772,10 +790,10 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>8</v>
@@ -784,7 +802,7 @@
         <v>32</v>
       </c>
       <c r="G4">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="H4">
         <v>7.5</v>
@@ -797,7 +815,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -835,10 +853,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -852,16 +870,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920399</v>
+        <v>19330051920436</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -870,6 +888,52 @@
         <v>11</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>19330051920393</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>19330051920399</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20221.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20221.xlsx
@@ -753,7 +753,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -779,7 +779,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20221.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20221.xlsx
@@ -805,7 +805,7 @@
         <v>76.19</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20221.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -76,37 +76,10 @@
     <t>BRETON</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
     <t>VICENTE</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>VERGEL</t>
-  </si>
-  <si>
     <t>AMYRA NAHOMY</t>
-  </si>
-  <si>
-    <t>ASTRID</t>
-  </si>
-  <si>
-    <t>ITZEL ISABEL</t>
-  </si>
-  <si>
-    <t>PAULINA</t>
   </si>
 </sst>
 </file>
@@ -559,19 +532,19 @@
         <v>42</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>8</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>76.19</v>
+        <v>80.95</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -676,19 +649,19 @@
         <v>42</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>8</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>76.19</v>
+        <v>80.95</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -793,16 +766,16 @@
         <v>42</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>76.19</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H4">
         <v>7.3</v>
@@ -815,7 +788,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -853,10 +826,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -866,75 +839,6 @@
       </c>
       <c r="G2">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920436</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920393</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920399</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
